--- a/artfynd/A 2464-2025 artfynd.xlsx
+++ b/artfynd/A 2464-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123361787</v>
+        <v>123361777</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507156</v>
+        <v>507147</v>
       </c>
       <c r="R2" t="n">
-        <v>6992394</v>
+        <v>6992387</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361777</v>
+        <v>123361787</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507147</v>
+        <v>507156</v>
       </c>
       <c r="R3" t="n">
-        <v>6992387</v>
+        <v>6992394</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2464-2025 artfynd.xlsx
+++ b/artfynd/A 2464-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>123361787</v>
       </c>
       <c r="B3" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2464-2025 artfynd.xlsx
+++ b/artfynd/A 2464-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123361777</v>
+        <v>123361787</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507147</v>
+        <v>507156</v>
       </c>
       <c r="R2" t="n">
-        <v>6992387</v>
+        <v>6992394</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361787</v>
+        <v>123361777</v>
       </c>
       <c r="B3" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507156</v>
+        <v>507147</v>
       </c>
       <c r="R3" t="n">
-        <v>6992394</v>
+        <v>6992387</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2464-2025 artfynd.xlsx
+++ b/artfynd/A 2464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123361777</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>123361787</v>
       </c>
       <c r="B3" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2464-2025 artfynd.xlsx
+++ b/artfynd/A 2464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123361777</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>123361787</v>
       </c>
       <c r="B3" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2464-2025 artfynd.xlsx
+++ b/artfynd/A 2464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123361777</v>
       </c>
       <c r="B2" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>123361787</v>
       </c>
       <c r="B3" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 2464-2025 artfynd.xlsx
+++ b/artfynd/A 2464-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123361777</v>
+        <v>123361787</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507147</v>
+        <v>507156</v>
       </c>
       <c r="R2" t="n">
-        <v>6992387</v>
+        <v>6992394</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361787</v>
+        <v>123361777</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507156</v>
+        <v>507147</v>
       </c>
       <c r="R3" t="n">
-        <v>6992394</v>
+        <v>6992387</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2464-2025 artfynd.xlsx
+++ b/artfynd/A 2464-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123361787</v>
+        <v>123361777</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507156</v>
+        <v>507147</v>
       </c>
       <c r="R2" t="n">
-        <v>6992394</v>
+        <v>6992387</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361777</v>
+        <v>123361787</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507147</v>
+        <v>507156</v>
       </c>
       <c r="R3" t="n">
-        <v>6992387</v>
+        <v>6992394</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2464-2025 artfynd.xlsx
+++ b/artfynd/A 2464-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123361777</v>
+        <v>123361787</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507147</v>
+        <v>507156</v>
       </c>
       <c r="R2" t="n">
-        <v>6992387</v>
+        <v>6992394</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361787</v>
+        <v>123361788</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507156</v>
+        <v>507086</v>
       </c>
       <c r="R3" t="n">
-        <v>6992394</v>
+        <v>6992321</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,6 +866,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123361777</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>507147</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6992387</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2464-2025 artfynd.xlsx
+++ b/artfynd/A 2464-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361787</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361788</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,8 +983,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361777</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>